--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0085.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0085.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Từ Khởi Đầu Đến Hiện Tại</t>
+          <t>Từ Khởi Đầu Đến Bây Giờ</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>The Shorekeeper's Rebirth</t>
+          <t>Sự Tái Sinh Của Người Gác Bờ</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Street Antique Appraisal</t>
+          <t>Định giá Đồ cổ Đường phố</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>A Returned Treasure</t>
+          <t>Kho Báu Trở Về</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Where History Endures</t>
+          <t>Nơi Lịch Sử Tồn Tại</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>The Ruyi Ring</t>
+          <t>Nhẫn Như Ý</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Chuyển Bản Đồ</t>
+          <t>Chuyển bản đồ</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Hoàn Thành Tactical Trials Tại 3 Địa Điểm Khác Nhau</t>
+          <t>Hoàn thành Thử Thách Chiến Thuật tại 3 địa điểm khác nhau</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Đạt 12.000 Điểm Trong Fairy Tale's Finale</t>
+          <t>Đạt 12.000 điểm trong Fairy Tale's Finale.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Đạt 2.000 Điểm Trong 3 Thử Thách Tương Ứng Trong Infinite Battle Simulation</t>
+          <t>Nhận 2.000 điểm ở 3 thử thách riêng biệt trong Infinite Battle Simulation.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Dùng Youhu Để Vượt Hazard Tower Tầng 1 &amp; Tầng 2 Trong "Tower of Adversity: Hazard Zone"</t>
+          <t>Dùng Youhu để vượt qua Tầng 1 và Tầng 2 Tháp Nguy Hiểm trong "Tháp Thử Thách: Vùng Nguy Hiểm".</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Đánh Bại Fallacy of Không Return 3 Lần</t>
+          <t>Đánh bại Fallacy of No Return 3 lần</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Đánh Bại Hedgepuff</t>
+          <t>Đánh bại Hedgepuff</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Đánh Bại Blazing Cutlass</t>
+          <t>Đánh bại Kiếm Khách Bùng Cháy</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Đánh Bại Cyclone</t>
+          <t>Đánh bại Cyclone</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Đánh Bại Tambourine Duo</t>
+          <t>Tiêu diệt Tambourine Duo</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Đánh Bại Nhà Vô Địch Alptop</t>
+          <t>Đánh bại Alptop Champion</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Sử dụng 6 Resonator khác nhau để hoàn thành bất kỳ độ khó nào của Phantasm Amass một lần</t>
+          <t>Hoàn thành Phantasm Amass ở bất kỳ độ khó nào một lần bằng 6 Resonator khác nhau.</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Clear Phantasm Amass IV</t>
+          <t>Hoàn thành Phantasm Amass IV</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Clear Phantasm Amass V</t>
+          <t>Hoàn thành Phantasm Amass V</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Clear Phantasm Amass VI</t>
+          <t>Hoàn thành Phantasm Amass VI</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Nhận tất cả phần thưởng Supply trong Beyond the Waves</t>
+          <t>Nhận tất cả phần thưởng Cung Ứng trong Beyond the Waves.</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Đạt 2600 điểm ở Giai đoạn 6 của Tactical Simulacra II</t>
+          <t>Đạt 2.600 điểm ở Giai Đoạn 6 của Tactical Simulacra II.</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Đạt 1200 điểm ở Giai đoạn 7 của Tactical Simulacra II</t>
+          <t>Đạt 1.200 điểm ở Giai Đoạn 7 của Tactical Simulacra II.</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Đạt 1000 điểm ở Endless Arena của Pincer Maneuver Warriors I</t>
+          <t>Đạt 1000 điểm trong Đấu Trường Vô Tận của Chiến Binh Chiến Thuật Kẹp I</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Đạt 2000 điểm ở Endless Arena của Pincer Maneuver Warriors I</t>
+          <t>Đạt 2.000 điểm trong Đấu Trường Vô Tận của Chiến Binh Pincer Maneuver I</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Đạt 1000 điểm ở Endless Arena của Pincer Maneuver Warriors II</t>
+          <t>Đạt 1000 điểm trong Đấu Trường Vô Tận của Chiến Binh Chiến Thuật Kẹp II</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Đạt 2000 điểm ở Endless Arena của Pincer Maneuver Warriors II</t>
+          <t>Đạt 2.000 điểm trong Đấu Trường Vô Tận của Chiến Binh Pincer Maneuver II</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Sử dụng Camellya để hoàn thành Tầng 1 &amp; Tầng 2 Hazard Tower trong "Tower of Adversity: Hazard Zone"</t>
+          <t>Dùng Camellya để vượt qua Tầng 1 &amp; Tầng 2 của Tháp Hazard trong "Tháp Nghịch Cảnh: Vùng Nguy Hiểm"</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Sử dụng Lumi để hoàn thành Tầng 1 &amp; Tầng 2 Hazard Tower trong "Tower of Adversity: Hazard Zone"</t>
+          <t>Dùng Lumi để vượt qua Tầng 1 &amp; Tầng 2 Tháp Nguy Hiểm trong "Tháp Nghịch Cảnh: Vùng Nguy Hiểm"</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Sử dụng Changli để hoàn thành Tầng 1 &amp; Tầng 2 Hazard Tower trong "Tower of Adversity: Hazard Zone"</t>
+          <t>Dùng Changli để vượt tầng 1 và 2 của Tháp Nguy Hiểm trong "Tower of Adversity: Hazard Zone"</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Quest and Event Test</t>
+          <t>Thử nghiệm Nhiệm vụ và Sự kiện</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Tower of Adversity Test</t>
+          <t>Bài Kiểm Tra Tháp Thử Thách</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Tactical Hologram Test</t>
+          <t>Thử Nghiệm Bản Hologram Chiến Thuật</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Phantasm Amass</t>
+          <t>Ảo Ảnh Hội Tụ</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Beyond the Waves</t>
+          <t>Vượt Qua Những Con Sóng</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Mô phỏng Chiến thuật</t>
+          <t>Bản Sao Chiến Thuật</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Bank of Life: Tầng 1</t>
+          <t>Ngân Hàng Sự Sống: Tầng 1</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Bank of Life: Tầng 2</t>
+          <t>Ngân Hàng Sự Sống: Tầng 2</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Error Cell: Lower Floor</t>
+          <t>Lỗi Tế bào: Tầng Dưới</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Error Cell: Upper Floor</t>
+          <t>Lỗi Tế bào: Tầng Trên</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Mysterious Room</t>
+          <t>Căn Phòng Bí Ẩn</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>First Clear Completed</t>
+          <t>Hoàn Thành Lần Đầu Tiên</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Phần thưởng hoàn thành lần đầu</t>
+          <t>Phần Thưởng Lần Đầu Vượt Ải</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Rương Cung Cấp</t>
+          <t>Supply Chest</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Default</t>
+          <t>Mặc định</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Nightmares Have Sealed Your Strengths</t>
+          <t>Ác Mộng Đã Phong Ấn Sức Mạnh Của Ngươi</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>Đi thôi</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>Đi thôi</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Insufficient Adventure Logs</t>
+          <t>Nhật Ký Phiêu Lưu không đủ</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Vòng này vẫn đang bị khóa</t>
+          <t>Lượt này vẫn đang bị khóa.</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Vui lòng hoàn thành vòng trước</t>
+          <t>Hãy hoàn thành vòng trước đã</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Vòng này sẽ được mở khóa sau 1 phút</t>
+          <t>Vòng này sẽ được mở trong 1 phút nữa</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Daily</t>
+          <t>Hoạt động hàng ngày</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Daily</t>
+          <t>Hoạt động hàng ngày</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Đăng nhập để nhận 2 Adventure Logs</t>
+          <t>Đăng nhập để nhận 2 Nhật Ký Phiêu Lưu</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Đã nhận tất cả</t>
+          <t>Đã nhận hết</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Giấc Mơ Không Xác Định</t>
+          <t>Giấc Mộng Vô Định</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Vui lòng chọn 3 Resonator để bắt đầu thử thách</t>
+          <t>Hãy chọn 3 Resonator để bắt đầu thử thách.</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Giai đoạn 1</t>
+          <t>Giai Đoạn 1</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Giai đoạn 2</t>
+          <t>Giai Đoạn 2</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Giai đoạn 3</t>
+          <t>Giai Đoạn 3</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Giai đoạn 4</t>
+          <t>Giai Đoạn 4</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Giai đoạn 5</t>
+          <t>Giai Đoạn 5</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Giai đoạn 6</t>
+          <t>Giai Đoạn 6</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Giai đoạn 7</t>
+          <t>Giai Đoạn 7</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Stellar Journey</t>
+          <t>Hành Trình Tinh Tú</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Cosmical Forge</t>
+          <t>Lò Rèn Vũ Trụ</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Consonant Echoes</t>
+          <t>Âm Vang Đồng Âm</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Điểm cao nhất: -</t>
+          <t>Điểm Cao Nhất: -</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Nightmares Have Trapped Your Companions</t>
+          <t>Ác Mộng Đã Giam Cầm Đồng Đội Của Ngươi</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Yu Hye Ji</t>
+          <t>Dư Huệ Chi</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Không xác định</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Nữ</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Lollo Logistics</t>
+          <t>Lollo Hậu Cần</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Kaleido Refraction</t>
+          <t>Khúc Xạ Đa Sắc</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Jing Chen</t>
+          <t>Tinh Trần</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Hướng tới những ngày phía trước</t>
+          <t>Tới Những Ngày Phía Trước</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Labyrinth</t>
+          <t>Mê Cung</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>A Fleeting Moment</t>
+          <t>Một Khoảnh Khắc Phù Du</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Ngày xửa ngày xưa</t>
+          <t>Ngày Xửa Ngày Xưa</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Mountain Memories</t>
+          <t>Ký Ức Núi Non</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Hướng về chân trời</t>
+          <t>Hướng Về Chân Trời</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -7504,7 +7504,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Neon City</t>
+          <t>Thành phố Neon</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Vượt sông băng núi</t>
+          <t>Vượt Sông Vượt Núi</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Trên đường đi</t>
+          <t>Trên đường phiêu lưu</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Wooden Doll</t>
+          <t>Búp bê gỗ</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Spectrum Bracelet</t>
+          <t>Vòng Tay Phổ Quang</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>A Camellia</t>
+          <t>Một bông hoa Trà Mi</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -16044,7 +16044,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Lollo Marker</t>
+          <t>Mốc Lollo</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
@@ -16114,7 +16114,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Navigator Baton</t>
+          <t>Gậy Điều Hướng</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
@@ -16184,7 +16184,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Squeakie Plushie</t>
+          <t>Gấu bông Chít Chít</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
@@ -16394,7 +16394,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Độ khó III</t>
+          <t>Độ Khó III</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
@@ -16464,7 +16464,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Độ khó IV</t>
+          <t>Độ Khó IV</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -16534,7 +16534,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Độ khó V</t>
+          <t>Độ Khó V</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
@@ -16604,7 +16604,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Độ khó VI</t>
+          <t>Độ Khó VI</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Không thể thay đổi Echo ở trạng thái Sẵn sàng</t>
+          <t>Không thể thay đổi Echo khi ở trạng thái Sẵn Sàng</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
@@ -16884,7 +16884,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Thử thách lại</t>
+          <t>Thử Thách Lại</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
@@ -16954,7 +16954,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Time Taken</t>
+          <t>Thời gian đã trôi qua</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -17024,7 +17024,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Mê Cung Giấc Mộng</t>
+          <t>Mê Cung Somnium</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -17094,7 +17094,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Hành Trình Giấc Mộng</t>
+          <t>Hành Trình Mộng Ảo</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Kẻ Đuổi Theo Vết Nứt</t>
+          <t>Kẻ Đột Kích Hư Không</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
@@ -17234,7 +17234,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Ác mộng quay lại</t>
+          <t>Ác Mộng Quay Trở Lại</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -17514,7 +17514,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Hiện không theo dõi điểm đánh dấu bản đồ nào</t>
+          <t>Hiện không theo dõi bất kỳ điểm đánh dấu nào trên bản đồ</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
@@ -17654,7 +17654,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Mở khóa sau khi hoàn thành "When the Night Knocks"</t>
+          <t>Mở sau khi hoàn thành "Khi Bóng Đêm Gõ Cửa"</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -17724,7 +17724,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Mở khóa sau khi vượt qua độ khó trước đó</t>
+          <t>Mở sau khi hoàn thành độ khó trước</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
@@ -17794,7 +17794,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Mở khóa sau khi vượt qua độ khó trước đó</t>
+          <t>Mở sau khi hoàn thành độ khó trước</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -17864,7 +17864,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Mở khóa sau khi vượt qua độ khó trước đó</t>
+          <t>Mở sau khi hoàn thành độ khó trước</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
@@ -17934,7 +17934,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Mở khóa sau khi vượt qua độ khó trước đó</t>
+          <t>Mở sau khi hoàn thành độ khó trước</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -18004,7 +18004,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Mở khóa sau khi vượt qua độ khó trước đó</t>
+          <t>Mở sau khi hoàn thành độ khó trước</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
@@ -18074,7 +18074,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Tiếp tục nhiệm vụ "When the Night Knocks" để mở khóa</t>
+          <t>Tiếp tục nhiệm vụ "Khi Bóng Đêm Gõ Cửa" để mở khóa</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -18144,7 +18144,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Tiếp tục nhiệm vụ "When the Night Knocks" để mở khóa</t>
+          <t>Tiếp tục nhiệm vụ "Khi Bóng Đêm Gõ Cửa" để mở khóa</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -18214,7 +18214,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Tiếp tục nhiệm vụ "When the Night Knocks" để mở khóa</t>
+          <t>Tiếp tục nhiệm vụ "Khi Bóng Đêm Gõ Cửa" để mở khóa</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
@@ -18284,7 +18284,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Tiếp tục nhiệm vụ "When the Night Knocks" để mở khóa</t>
+          <t>Tiếp tục nhiệm vụ "Khi Bóng Đêm Gõ Cửa" để mở khóa</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>Tiếp tục nhiệm vụ "When the Night Knocks" để mở khóa</t>
+          <t>Tiếp tục nhiệm vụ "Khi Bóng Đêm Gõ Cửa" để mở khóa</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
@@ -18425,7 +18425,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Enter Serial Không: MLCL190468] 
+          <t xml:space="preserve">[Nhập Số Seri: MLCL190468]
 </t>
         </is>
       </c>
@@ -18497,7 +18497,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Averardo Vault - Inventory Records]
+          <t xml:space="preserve">Hồ sơ Kho Averardo - Biên bản Kiểm kê
 </t>
         </is>
       </c>
@@ -18569,7 +18569,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vật phẩm: Đèn Terminal (Bao gồm Mô-đun Dữ liệu Lõi có thể tháo rời)
+          <t xml:space="preserve">Vật phẩm: Thiết bị đầu cuối dạng đèn lồng (Bao gồm Mô-đun Dữ liệu Nhân lõi có thể tháo rời)
 </t>
         </is>
       </c>
@@ -18641,7 +18641,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t xml:space="preserve">Retrieval Log:
+          <t xml:space="preserve">Nhật Ký Thu Thập:
 </t>
         </is>
       </c>
@@ -18782,7 +18782,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Trang phục Preview</t>
+          <t>Xem Trước Trang Phục</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -18922,7 +18922,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>Đi thôi</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
@@ -18992,7 +18992,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm vụ Chính "To the Shore's End" để có trải nghiệm tốt hơn</t>
+          <t>Hoàn thành Nhiệm Vụ Chính "Tận Cùng Bờ Vực" để có trải nghiệm tốt hơn</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -19062,7 +19062,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Early Access Available</t>
+          <t>Truy Cập Sớm Đã Mở</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
@@ -19132,7 +19132,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Proceed</t>
+          <t>Tiến lên</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
@@ -19202,7 +19202,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Đến Rinascita ngay?</t>
+          <t>Đến Rinascita luôn à?</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
@@ -19342,7 +19342,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Phần thưởng Xu</t>
+          <t>Phần Thưởng Xu</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
@@ -19412,7 +19412,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Coins Collected</t>
+          <t>Xu Thu Thập Được</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -19482,7 +19482,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Vật liệu trong Hàng hóa đã được chuyển đổi thành vật phẩm trong Túi đồ</t>
+          <t>Vật liệu trong Hàng Hóa đã được chuyển vào Túi Đồ.</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -19552,7 +19552,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Không thể đặt loại vật phẩm này</t>
+          <t>Không thể đặt loại vật phẩm này vào đây.</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -19622,7 +19622,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Vui lòng xử lý vật phẩm đã chọn trước</t>
+          <t>Trước tiên, hãy xử lý món đồ đã chọn đi.</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
@@ -19692,7 +19692,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Không thể đặt ở đây</t>
+          <t>Không thể đặt nó ở đây được.</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -19762,7 +19762,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Đã đáp ứng điều kiện Bán Nhanh</t>
+          <t>Đã đủ điều kiện bán nhanh</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -19832,7 +19832,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Bán Nhanh hoàn tất</t>
+          <t>Hoàn tất bán nhanh</t>
         </is>
       </c>
       <c r="N277" t="inlineStr">
@@ -19902,7 +19902,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Vui lòng kiểm tra tại bến tàu</t>
+          <t>Hãy kiểm tra nó ở bến tàu</t>
         </is>
       </c>
       <c r="N278" t="inlineStr">
@@ -19972,7 +19972,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Vật phẩm đã được giao</t>
+          <t>Đã giao vật phẩm</t>
         </is>
       </c>
       <c r="N279" t="inlineStr">
@@ -20042,7 +20042,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Có thể phát hiện sau khi mở khóa mục này hoặc Mutant của nó</t>
+          <t>Có thể phát hiện sau khi mở khóa mục này hoặc Mutant của nó.</t>
         </is>
       </c>
       <c r="N280" t="inlineStr">
@@ -20112,7 +20112,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Loài gốc được tự động phát hiện</t>
+          <t>Loài gốc được tự động phát hiện.</t>
         </is>
       </c>
       <c r="N281" t="inlineStr">
@@ -20182,7 +20182,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Yêu cầu Wonder Bubble</t>
+          <t>Cần có Bong Bóng Kỳ Diệu</t>
         </is>
       </c>
       <c r="N282" t="inlineStr">
@@ -20252,7 +20252,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Isle Wanderings</t>
+          <t>Lang Thang Trên Đảo</t>
         </is>
       </c>
       <c r="N283" t="inlineStr">
@@ -20322,7 +20322,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Những cuộc phiêu lưu ở Thành phố Nước</t>
+          <t>Phiêu Lưu Tại Thành Phố Nước</t>
         </is>
       </c>
       <c r="N284" t="inlineStr">
@@ -20392,7 +20392,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>The Envoys' Roll</t>
+          <t>Danh Sách Các Sứ Giả</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
@@ -20462,7 +20462,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Giữa biển mây</t>
+          <t>Giữa Biển Mây</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
@@ -20532,7 +20532,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Nâng cấp để mở khóa thử thách "Giữa biển mây"</t>
+          <t>Nâng cấp để mở khóa thử thách "Giữa Biển Mây"</t>
         </is>
       </c>
       <c r="N287" t="inlineStr">
@@ -20602,7 +20602,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Nâng cấp để mở khóa thử thách "Giữa biển mây"</t>
+          <t>Nâng cấp để mở khóa thử thách "Giữa Biển Mây"</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">
@@ -20672,7 +20672,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Nâng cấp để mở khóa thử thách "Giữa biển mây"</t>
+          <t>Nâng cấp để mở khóa thử thách "Giữa Biển Mây"</t>
         </is>
       </c>
       <c r="N289" t="inlineStr">
@@ -20742,7 +20742,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Nâng cấp để mở khóa thử thách "Giữa biển mây"</t>
+          <t>Nâng cấp để mở khóa thử thách "Giữa Biển Mây"</t>
         </is>
       </c>
       <c r="N290" t="inlineStr">
@@ -20812,7 +20812,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Nâng cấp để mở khóa thử thách "Giữa biển mây"</t>
+          <t>Nâng cấp để mở khóa thử thách "Giữa Biển Mây"</t>
         </is>
       </c>
       <c r="N291" t="inlineStr">
@@ -20882,7 +20882,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Nâng cấp để mở khóa thử thách "Giữa biển mây"</t>
+          <t>Nâng cấp để mở khóa thử thách "Giữa Biển Mây"</t>
         </is>
       </c>
       <c r="N292" t="inlineStr">
@@ -20952,7 +20952,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Nâng cấp để mở khóa thử thách "Giữa biển mây"</t>
+          <t>Nâng cấp để mở khóa thử thách "Giữa Biển Mây"</t>
         </is>
       </c>
       <c r="N293" t="inlineStr">
@@ -21022,7 +21022,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>[Thử thách Echo: Bay I] Đã mở khóa</t>
+          <t>[Thử Thách Tiếng Vọng: Bay Cấp I] Đã mở khóa</t>
         </is>
       </c>
       <c r="N294" t="inlineStr">
@@ -21092,7 +21092,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>[Thử thách Echo: Bay II] Đã mở khóa</t>
+          <t>[Thử Thách Tiếng Vọng: Bay Cấp II] Đã mở khóa</t>
         </is>
       </c>
       <c r="N295" t="inlineStr">
@@ -21162,7 +21162,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>[Thử thách Echo: Bay III] Đã mở khóa</t>
+          <t>[Thử Thách Tiếng Vọng: Bay Cấp III] Đã mở khóa</t>
         </is>
       </c>
       <c r="N296" t="inlineStr">
@@ -21232,7 +21232,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>[Thử thách Echo: Bay IV] Đã mở khóa</t>
+          <t>[Thử Thách Tiếng Vọng: Bay Cấp IV] Đã mở khóa</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
@@ -21302,7 +21302,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>[Thử thách Echo: Bay V] Đã mở khóa</t>
+          <t>Thử Thách Tiếng Vọng: Bay Cấp V Đã Mở Khóa</t>
         </is>
       </c>
       <c r="N298" t="inlineStr">
@@ -21372,7 +21372,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>[Thử thách Echo: Bay VI] Đã mở khóa</t>
+          <t>Thử Thách Tiếng Vọng: Bay Cấp VI Đã Mở Khóa</t>
         </is>
       </c>
       <c r="N299" t="inlineStr">
@@ -21442,7 +21442,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>[Thử thách Echo: Bay VII] Đã mở khóa</t>
+          <t>Thử Thách Tiếng Vọng: Bay Cấp VII Đã Mở Khóa</t>
         </is>
       </c>
       <c r="N300" t="inlineStr">
@@ -21512,7 +21512,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>[Thử thách Echo: Bay I]</t>
+          <t>[Thử Thách Tiếng Vọng: Bay Cấp I]</t>
         </is>
       </c>
       <c r="N301" t="inlineStr">
@@ -21582,7 +21582,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>[Thử thách Echo: Bay II]</t>
+          <t>[Thử Thách Tiếng Vọng: Bay Cấp II]</t>
         </is>
       </c>
       <c r="N302" t="inlineStr">
@@ -21652,7 +21652,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>[Echo Challenge: Flight III]</t>
+          <t>[Thử Thách Tiếng Vọng: Bay Cấp III]</t>
         </is>
       </c>
       <c r="N303" t="inlineStr">
@@ -21722,7 +21722,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>[Echo Challenge: Flight IV]</t>
+          <t>[Thử Thách Tiếng Vọng: Bay Cấp IV]</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
@@ -21792,7 +21792,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>[Echo Challenge: Flight V]</t>
+          <t>Thử Thách Tiếng Vọng: Bay Cấp V</t>
         </is>
       </c>
       <c r="N305" t="inlineStr">
@@ -21862,7 +21862,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>[Echo Challenge: Flight VI]</t>
+          <t>Thử Thách Tiếng Vọng: Bay Cấp VI</t>
         </is>
       </c>
       <c r="N306" t="inlineStr">
@@ -21932,7 +21932,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>[Echo Challenge: Flight VII]</t>
+          <t>Thử Thách Tiếng Vọng: Bay Cấp VII</t>
         </is>
       </c>
       <c r="N307" t="inlineStr">
@@ -22002,7 +22002,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Hadrian's Gladiator</t>
+          <t>Đấu sĩ của Hadrian</t>
         </is>
       </c>
       <c r="N308" t="inlineStr">
@@ -22142,7 +22142,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Aria Mummer</t>
+          <t>Diễn Viên Aria</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
@@ -22422,7 +22422,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Farceur's Faces</t>
+          <t>Những Gương Mặt Hề Giả</t>
         </is>
       </c>
       <c r="N314" t="inlineStr">
@@ -22562,7 +22562,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Signor Octopus</t>
+          <t>Ngài Bạch Tuộc</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
@@ -22702,7 +22702,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>Plushie Squad</t>
+          <t>Đội Bông Gòn</t>
         </is>
       </c>
       <c r="N318" t="inlineStr">
@@ -22842,7 +22842,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Đạt hạng S</t>
+          <t>Đạt Hạng S</t>
         </is>
       </c>
       <c r="N320" t="inlineStr">
@@ -22912,7 +22912,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>Đạt hạng A</t>
+          <t>Đạt Hạng A</t>
         </is>
       </c>
       <c r="N321" t="inlineStr">
@@ -22982,7 +22982,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Đạt hạng B</t>
+          <t>Đạt Hạng B</t>
         </is>
       </c>
       <c r="N322" t="inlineStr">
@@ -23052,7 +23052,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Nâng cấp cấp độ sự kiện lên 1</t>
+          <t>Nâng cấp sự kiện lên cấp 1</t>
         </is>
       </c>
       <c r="N323" t="inlineStr">
@@ -23122,7 +23122,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Nâng cấp cấp độ sự kiện lên 2</t>
+          <t>Nâng cấp sự kiện lên cấp 2</t>
         </is>
       </c>
       <c r="N324" t="inlineStr">
@@ -23192,7 +23192,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Nâng cấp cấp độ sự kiện lên 3</t>
+          <t>Nâng cấp sự kiện lên cấp 3</t>
         </is>
       </c>
       <c r="N325" t="inlineStr">
@@ -23262,7 +23262,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Nâng cấp cấp độ sự kiện lên 4</t>
+          <t>Nâng cấp sự kiện lên cấp 4</t>
         </is>
       </c>
       <c r="N326" t="inlineStr">
@@ -23332,7 +23332,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Nâng cấp cấp độ sự kiện lên 5</t>
+          <t>Nâng Cấp Sự Kiện lên Cấp 5</t>
         </is>
       </c>
       <c r="N327" t="inlineStr">
@@ -23402,7 +23402,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Nâng cấp cấp độ sự kiện lên 6</t>
+          <t>Nâng Cấp Sự Kiện lên Cấp 6</t>
         </is>
       </c>
       <c r="N328" t="inlineStr">
@@ -23472,7 +23472,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Chuyện kể trên đảo</t>
+          <t>Huyền Thoại Quần Đảo</t>
         </is>
       </c>
       <c r="N329" t="inlineStr">
@@ -23542,7 +23542,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Claimed</t>
+          <t>Đã nhận</t>
         </is>
       </c>
       <c r="N330" t="inlineStr">
@@ -23612,7 +23612,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Đã đạt cấp độ tối đa</t>
+          <t>Đã đạt cấp tối đa</t>
         </is>
       </c>
       <c r="N331" t="inlineStr">
@@ -23682,7 +23682,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>Đi thôi</t>
         </is>
       </c>
       <c r="N332" t="inlineStr">
@@ -23892,7 +23892,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Có thể nâng cấp</t>
+          <t>Có thể Nâng Cấp</t>
         </is>
       </c>
       <c r="N335" t="inlineStr">
@@ -24032,7 +24032,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>Đi thôi</t>
         </is>
       </c>
       <c r="N337" t="inlineStr">
@@ -24172,7 +24172,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Đến Thế Giới Mới</t>
+          <t>Tới Thế Giới Mới</t>
         </is>
       </c>
       <c r="N339" t="inlineStr">
@@ -24242,7 +24242,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Đi Sâu Vào Lòng Đất</t>
+          <t>Vào Vực Sâu</t>
         </is>
       </c>
       <c r="N340" t="inlineStr">
@@ -24312,7 +24312,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Xuyên Qua Màn Tĩnh Lặng</t>
+          <t>Xuyên qua Màn Tĩnh Lặng</t>
         </is>
       </c>
       <c r="N341" t="inlineStr">
@@ -24382,7 +24382,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Thức Tỉnh Của Một Thế Giới</t>
+          <t>Sự Thức Tỉnh Của Thế Giới</t>
         </is>
       </c>
       <c r="N342" t="inlineStr">
@@ -24452,7 +24452,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Daydream Lullaby</t>
+          <t>Khúc Ru Giấc Mơ</t>
         </is>
       </c>
       <c r="N343" t="inlineStr">
@@ -24522,7 +24522,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>The Waves Play On</t>
+          <t>Âm Vang Của Sóng</t>
         </is>
       </c>
       <c r="N344" t="inlineStr">
@@ -24592,7 +24592,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Duplicitous Tower</t>
+          <t>Tháp Song Trùng</t>
         </is>
       </c>
       <c r="N345" t="inlineStr">
@@ -24662,7 +24662,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Saving Light</t>
+          <t>Ánh Sáng Cứu Rỗi</t>
         </is>
       </c>
       <c r="N346" t="inlineStr">
@@ -24732,7 +24732,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Mây Ngàn Năm Tan Biến</t>
+          <t>Vân Vạn Kiếp Nâng Cao</t>
         </is>
       </c>
       <c r="N347" t="inlineStr">
@@ -24802,7 +24802,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>In Three Days' Time</t>
+          <t>Ba Ngày Tới</t>
         </is>
       </c>
       <c r="N348" t="inlineStr">
@@ -24872,7 +24872,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Đồng Cỏ Như Ngày Xưa</t>
+          <t>Cánh Đồng Xưa</t>
         </is>
       </c>
       <c r="N349" t="inlineStr">
@@ -24942,7 +24942,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Wilderness Wanderer</t>
+          <t>Lữ Khách Hoang Dã</t>
         </is>
       </c>
       <c r="N350" t="inlineStr">
@@ -25012,7 +25012,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Mùa Xuân Tràn Ngập</t>
+          <t>Xuân Đang Rộn Ràng</t>
         </is>
       </c>
       <c r="N351" t="inlineStr">
@@ -25082,7 +25082,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Prophet's Message</t>
+          <t>Thông Điệp Từ Nhà Tiên Tri</t>
         </is>
       </c>
       <c r="N352" t="inlineStr">
@@ -25152,7 +25152,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Cuộc Hẹn Trên Núi</t>
+          <t>Hẹn Gặp Trên Núi</t>
         </is>
       </c>
       <c r="N353" t="inlineStr">
@@ -25222,7 +25222,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Daybreak Descends</t>
+          <t>Bình Minh Giáng Lâm</t>
         </is>
       </c>
       <c r="N354" t="inlineStr">
@@ -25292,7 +25292,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>Vast Lush Grounds</t>
+          <t>Đất Rộng Xanh Tươi</t>
         </is>
       </c>
       <c r="N355" t="inlineStr">
@@ -25362,7 +25362,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Rowing Towards Firmament</t>
+          <t>Chèo Về Chân Trời Kiên Cố</t>
         </is>
       </c>
       <c r="N356" t="inlineStr">
@@ -25432,7 +25432,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Daybreak Arises</t>
+          <t>Bình Minh Ló Dạng</t>
         </is>
       </c>
       <c r="N357" t="inlineStr">
@@ -25572,7 +25572,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>De Anima / Về Linh Hồn</t>
+          <t>Về Linh Hồn</t>
         </is>
       </c>
       <c r="N359" t="inlineStr">
@@ -25712,7 +25712,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>De Caelo / Về Bầu Trời</t>
+          <t>Về Bầu Trời</t>
         </is>
       </c>
       <c r="N361" t="inlineStr">
@@ -25782,7 +25782,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Astrum Unicum / Những Vì Sao, Sự Tái Sinh và Bạn</t>
+          <t>Astrum Unicum / Sao Trời, Tái Sinh và Ngươi</t>
         </is>
       </c>
       <c r="N362" t="inlineStr">
@@ -25852,7 +25852,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Ngày Tận Thế</t>
+          <t>Thế Giới Tận Diệt</t>
         </is>
       </c>
       <c r="N363" t="inlineStr">
@@ -25922,7 +25922,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Echoes of Destruction</t>
+          <t>Echo của sự Hủy diệt</t>
         </is>
       </c>
       <c r="N364" t="inlineStr">
@@ -25992,7 +25992,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>De Generatione et Corruptione / Về Sự Sinh Thành và Hủy Diệt</t>
+          <t>Về Sinh Thành và Hủy Diệt</t>
         </is>
       </c>
       <c r="N365" t="inlineStr">
@@ -26062,7 +26062,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Bài Ca KU-Roro</t>
+          <t>Khúc hát KU-Roro</t>
         </is>
       </c>
       <c r="N366" t="inlineStr">
@@ -26132,7 +26132,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>De Sophisticis Elenchis / Sophistical Refutations</t>
+          <t>Phản Bác Ngụy Biện</t>
         </is>
       </c>
       <c r="N367" t="inlineStr">
@@ -26202,7 +26202,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Nơi Trú Ẩn Của Những Người Sống Sót</t>
+          <t>Nơi trú ẩn của những người sống sót</t>
         </is>
       </c>
       <c r="N368" t="inlineStr">
@@ -26272,7 +26272,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Tất Cả Những Câu Chuyện Được Tìm Thấy Lại</t>
+          <t>Tất cả những Truyện Cổ Tích Được Tìm Thấy</t>
         </is>
       </c>
       <c r="N369" t="inlineStr">
@@ -26342,7 +26342,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>A Glance Backward</t>
+          <t>Nhìn Lại Quá Khứ</t>
         </is>
       </c>
       <c r="N370" t="inlineStr">
@@ -26412,7 +26412,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Vũ Công Giữa Muôn Hoa</t>
+          <t>Vũ công giữa muôn hoa</t>
         </is>
       </c>
       <c r="N371" t="inlineStr">
@@ -26482,7 +26482,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Sự Thay Đổi Bất Chợt Của Cuộc Đời</t>
+          <t>Sự Vô Thường Của Cuộc Đời</t>
         </is>
       </c>
       <c r="N372" t="inlineStr">
@@ -26552,7 +26552,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Hạt Giống Thuần Khiết</t>
+          <t>Hạt giống Thuần Khiết</t>
         </is>
       </c>
       <c r="N373" t="inlineStr">
@@ -26622,7 +26622,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Vortex</t>
+          <t>Xoáy Lốc</t>
         </is>
       </c>
       <c r="N374" t="inlineStr">
@@ -26692,7 +26692,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Khi Hoa Trà Đỏ Máu</t>
+          <t>Khi hoa trà nhuốm máu</t>
         </is>
       </c>
       <c r="N375" t="inlineStr">
@@ -26762,7 +26762,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Before I Wither</t>
+          <t>Trước Khi Ta Tàn Phai</t>
         </is>
       </c>
       <c r="N376" t="inlineStr">
@@ -26832,7 +26832,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Fleeting Sorrow</t>
+          <t>Sầu Phù Du</t>
         </is>
       </c>
       <c r="N377" t="inlineStr">
@@ -26902,7 +26902,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Everlasting Longing</t>
+          <t>Nỗi Nhớ Vĩnh Hằng</t>
         </is>
       </c>
       <c r="N378" t="inlineStr">
@@ -27042,7 +27042,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Wind-kissed Haven</t>
+          <t>Thiên Đường Gió Lay</t>
         </is>
       </c>
       <c r="N380" t="inlineStr">
@@ -27182,7 +27182,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>The Idyllic Refuge</t>
+          <t>Nơi Bình Yên Ảo Ảnh</t>
         </is>
       </c>
       <c r="N382" t="inlineStr">
@@ -27252,7 +27252,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Where Wind Whispers</t>
+          <t>Nơi Gió Thì Thầm</t>
         </is>
       </c>
       <c r="N383" t="inlineStr">
@@ -27322,7 +27322,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>The Midnight Elegy</t>
+          <t>Khúc Bi Ca Nửa Đêm</t>
         </is>
       </c>
       <c r="N384" t="inlineStr">
@@ -27392,7 +27392,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Waves Sing Goodnight</t>
+          <t>Làn Sóng Ru Giấc</t>
         </is>
       </c>
       <c r="N385" t="inlineStr">
@@ -27462,7 +27462,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Cứu Tôi Khỏi Những Con Sóng Đời Thường</t>
+          <t>Cứu Ta Khỏi Biển Trần Tục</t>
         </is>
       </c>
       <c r="N386" t="inlineStr">
@@ -27602,7 +27602,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Bức Màn Lên Cho Những Điều Mơ Mộng</t>
+          <t>Bắt đầu màn mộng tưởng</t>
         </is>
       </c>
       <c r="N388" t="inlineStr">
@@ -27742,7 +27742,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Lạc Lối Trên Con Đường Hành Hương</t>
+          <t>Lạc Trên Con Đường Hành Hương</t>
         </is>
       </c>
       <c r="N390" t="inlineStr">
@@ -27812,7 +27812,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Khi Đêm Nghỉ Trên Vách Đá</t>
+          <t>Khi Bóng Đêm Buông Xuống Vách Đá</t>
         </is>
       </c>
       <c r="N391" t="inlineStr">
@@ -27882,7 +27882,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Đắm tàu và Mắc cạn</t>
+          <t>Mắc Cạn và Bơ Vơ</t>
         </is>
       </c>
       <c r="N392" t="inlineStr">
@@ -27952,7 +27952,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Như Lời Thần Linh Phán</t>
+          <t>Như Lời Thần Đã Phán</t>
         </is>
       </c>
       <c r="N393" t="inlineStr">
@@ -28022,7 +28022,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Cloudcasting Project</t>
+          <t>Dự Án Cloudcasting</t>
         </is>
       </c>
       <c r="N394" t="inlineStr">
@@ -28232,7 +28232,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Gondola's Journey</t>
+          <t>Hành Trình Gondola</t>
         </is>
       </c>
       <c r="N397" t="inlineStr">
@@ -28302,7 +28302,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>The Nimbus Chorale</t>
+          <t>Dàn Hợp Xướng Nimbus</t>
         </is>
       </c>
       <c r="N398" t="inlineStr">
@@ -28372,7 +28372,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Khúc Ca của Những Kẻ Ngốc</t>
+          <t>Khúc hát của Những Kẻ Ngốc Nghếch</t>
         </is>
       </c>
       <c r="N399" t="inlineStr">
@@ -28442,7 +28442,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Khi Đêm Chìm vào Vực Thẳm</t>
+          <t>Khi Bóng Đêm Chìm Vào Vực Thẳm</t>
         </is>
       </c>
       <c r="N400" t="inlineStr">
@@ -28512,7 +28512,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Hiệu Quả là Sự Giàu Có</t>
+          <t>Hiệu Suất Là Sức Mạnh</t>
         </is>
       </c>
       <c r="N401" t="inlineStr">
@@ -28582,7 +28582,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Merry Plushie Bạn bè</t>
+          <t>Những Người Bạn Thú Nhồi Bông Vui Vẻ</t>
         </is>
       </c>
       <c r="N402" t="inlineStr">
@@ -28652,7 +28652,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Dancing Through Fantasies</t>
+          <t>Nhảy Qua Ảo Giác</t>
         </is>
       </c>
       <c r="N403" t="inlineStr">
@@ -28722,7 +28722,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Khúc Dạ Tình Dạt Dào Theo Sóng</t>
+          <t>Khúc Tình Ca Trên Sóng</t>
         </is>
       </c>
       <c r="N404" t="inlineStr">
@@ -28792,7 +28792,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Hành Trình Kết Thúc Trong Sóng Biển</t>
+          <t>Hành Trình Kết Thúc Trong Bóng Tối</t>
         </is>
       </c>
       <c r="N405" t="inlineStr">
@@ -28862,7 +28862,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Homebound Hour</t>
+          <t>Giờ Về Nhà</t>
         </is>
       </c>
       <c r="N406" t="inlineStr">
@@ -28932,7 +28932,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Khúc Aria của Sự Tha Thứ</t>
+          <t>Aria của Sự Tha Thứ</t>
         </is>
       </c>
       <c r="N407" t="inlineStr">
@@ -29002,7 +29002,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>A Fairy Tale</t>
+          <t>Một Câu Chuyện Cổ Tích</t>
         </is>
       </c>
       <c r="N408" t="inlineStr">
@@ -29072,7 +29072,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Ngọn Lửa Vẫn Rực Cháy</t>
+          <t>Ngọn Lửa Trường Tồn</t>
         </is>
       </c>
       <c r="N409" t="inlineStr">
@@ -29212,7 +29212,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>Thời Gian là Tiền Bạc</t>
+          <t>Thời gian là Vàng bạc</t>
         </is>
       </c>
       <c r="N411" t="inlineStr">
@@ -29282,7 +29282,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Entwined Footsteps</t>
+          <t>Bước chân hòa điệu</t>
         </is>
       </c>
       <c r="N412" t="inlineStr">
@@ -29352,7 +29352,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Silence's Treasure</t>
+          <t>Kho Báu Của Im Lặng</t>
         </is>
       </c>
       <c r="N413" t="inlineStr">
@@ -29422,7 +29422,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Lời Buộc Tội Kẻ Ăn Năn</t>
+          <t>Lời buộc tội của kẻ sám hối</t>
         </is>
       </c>
       <c r="N414" t="inlineStr">
@@ -29492,7 +29492,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Sự Phán Xét Dành Cho Kẻ Có Tội</t>
+          <t>Sự Trừng Phạt Dành Cho Kẻ Có Tội</t>
         </is>
       </c>
       <c r="N415" t="inlineStr">
@@ -29562,7 +29562,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Saving Light</t>
+          <t>Ánh Sáng Cứu Rỗi</t>
         </is>
       </c>
       <c r="N416" t="inlineStr">
@@ -29632,7 +29632,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Sự Thức Tỉnh của Thế Giới</t>
+          <t>Sự Thức Tỉnh Của Thế Giới</t>
         </is>
       </c>
       <c r="N417" t="inlineStr">
@@ -29702,7 +29702,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Sự Thức Tỉnh của Thế Giới</t>
+          <t>Sự Thức Tỉnh Của Thế Giới</t>
         </is>
       </c>
       <c r="N418" t="inlineStr">
@@ -29772,7 +29772,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Sự Thức Tỉnh của Thế Giới</t>
+          <t>Sự Thức Tỉnh Của Thế Giới</t>
         </is>
       </c>
       <c r="N419" t="inlineStr">
@@ -29842,7 +29842,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Sự Thức Tỉnh của Thế Giới</t>
+          <t>Sự Thức Tỉnh Của Thế Giới</t>
         </is>
       </c>
       <c r="N420" t="inlineStr">
@@ -29912,7 +29912,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>往岁乘霄</t>
+          <t>Những Năm Tháng Bay Cao</t>
         </is>
       </c>
       <c r="N421" t="inlineStr">
@@ -29982,7 +29982,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>過ぎし乗霄山の歳月</t>
+          <t>Những năm tháng đã qua trên núi Thừa Tiêu</t>
         </is>
       </c>
       <c r="N422" t="inlineStr">
@@ -30052,7 +30052,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Thawing Fates</t>
+          <t>Số Phận Tan Băng</t>
         </is>
       </c>
       <c r="N423" t="inlineStr">
@@ -30122,7 +30122,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>승소산의 메아리</t>
+          <t>Tiếng vọng từ núi Thăng Tiêu</t>
         </is>
       </c>
       <c r="N424" t="inlineStr">
@@ -30192,7 +30192,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>By Moon's Grace</t>
+          <t>Nhờ Ân Huệ của Mặt Trăng</t>
         </is>
       </c>
       <c r="N425" t="inlineStr">
@@ -30262,7 +30262,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>未尽之歌</t>
+          <t>Khúc ca chưa dứt</t>
         </is>
       </c>
       <c r="N426" t="inlineStr">
@@ -30332,7 +30332,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>未完成の歌</t>
+          <t>Bài ca chưa trọn</t>
         </is>
       </c>
       <c r="N427" t="inlineStr">
@@ -30402,7 +30402,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>An Unfinished Song</t>
+          <t>Khúc Ca Chưa Hoàn Thành</t>
         </is>
       </c>
       <c r="N428" t="inlineStr">
@@ -30472,7 +30472,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>끝나지 않는 노래</t>
+          <t>Bài ca bất tận</t>
         </is>
       </c>
       <c r="N429" t="inlineStr">
@@ -30542,7 +30542,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>一千万种可能</t>
+          <t>Một triệu khả năng khác nhau</t>
         </is>
       </c>
       <c r="N430" t="inlineStr">
@@ -30612,7 +30612,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>A Million Possibilities</t>
+          <t>Triệu Phương Án Khả Dĩ</t>
         </is>
       </c>
       <c r="N431" t="inlineStr">
@@ -30682,7 +30682,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Grand Feast Daydream</t>
+          <t>Giấc Mộng Đại Tiệc</t>
         </is>
       </c>
       <c r="N432" t="inlineStr">
@@ -30752,7 +30752,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Grand Feast Daydream (Special Edition)</t>
+          <t>Giấc Mộng Đại Tiệc (Bản Đặc Biệt)</t>
         </is>
       </c>
       <c r="N433" t="inlineStr">
@@ -30822,7 +30822,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>昼梦盛宴</t>
+          <t>Bữa tiệc ban ngày mộng mơ</t>
         </is>
       </c>
       <c r="N434" t="inlineStr">
@@ -30892,7 +30892,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>昼夢グランドフィースト</t>
+          <t>Grand Feast of Daydream</t>
         </is>
       </c>
       <c r="N435" t="inlineStr">
@@ -30962,7 +30962,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>꿈의 카니발</t>
+          <t>Lễ hội Carnival trong giấc mơ</t>
         </is>
       </c>
       <c r="N436" t="inlineStr">
@@ -31032,7 +31032,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Grand Feast Daydream (Instrumental)</t>
+          <t>Giấc Mộng Đại Tiệc (Bản Nhạc Không Lời)</t>
         </is>
       </c>
       <c r="N437" t="inlineStr">
@@ -31102,7 +31102,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>With Glory I Shall Fall</t>
+          <t>Ta Sẽ Ngã Xuống Trong Vinh Quang</t>
         </is>
       </c>
       <c r="N438" t="inlineStr">
@@ -31172,7 +31172,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Dây Lời Thề, Echo Lời Hứa</t>
+          <t>Dây Lời Thề, Tiếng Vọng Lời Hứa</t>
         </is>
       </c>
       <c r="N439" t="inlineStr">
@@ -31242,7 +31242,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Rippling Starlight</t>
+          <t>Ánh Sao Gợn Sáng</t>
         </is>
       </c>
       <c r="N440" t="inlineStr">
@@ -31312,7 +31312,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Suspended Twilight</t>
+          <t>Hoàng Hôn Lơ Lửng</t>
         </is>
       </c>
       <c r="N441" t="inlineStr">
@@ -31382,7 +31382,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Moonlit Solitude</t>
+          <t>Cô Đơn Dưới Trăng</t>
         </is>
       </c>
       <c r="N442" t="inlineStr">
@@ -31452,7 +31452,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Lạc giữa Biển Khơi</t>
+          <t>Lạc Trên Biển Cả</t>
         </is>
       </c>
       <c r="N443" t="inlineStr">
@@ -31522,7 +31522,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>The Second Departure</t>
+          <t>Khởi Hành Lần Hai</t>
         </is>
       </c>
       <c r="N444" t="inlineStr">
@@ -31592,7 +31592,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>Behind Gateway Thirty Three</t>
+          <t>Phía sau Cổng Ba Mươi Ba</t>
         </is>
       </c>
       <c r="N445" t="inlineStr">
@@ -31662,7 +31662,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Inside Pipe Sixty Six</t>
+          <t>Bên trong Đường Ống Số Sáu Mươi Sáu</t>
         </is>
       </c>
       <c r="N446" t="inlineStr">
@@ -31732,7 +31732,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Drowning Five Times Over</t>
+          <t>Chìm Đắm Năm Lần Liên Tiếp</t>
         </is>
       </c>
       <c r="N447" t="inlineStr">
@@ -31802,7 +31802,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Bảy Vũng Oan Nghiệt</t>
+          <t>Bảy Vực Ác</t>
         </is>
       </c>
       <c r="N448" t="inlineStr">
@@ -31872,7 +31872,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Risen Sau khi Eight Burials</t>
+          <t>Trỗi Dậy Sau Tám Lần An Táng</t>
         </is>
       </c>
       <c r="N449" t="inlineStr">
@@ -31942,7 +31942,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Beyond Ruin Nighty Nine</t>
+          <t>Vượt Qua Đêm Hủy Diệt Thứ Chín Mươi Chín</t>
         </is>
       </c>
       <c r="N450" t="inlineStr">
@@ -32012,7 +32012,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Bóng Ma Mười Tòa Tháp</t>
+          <t>Phantom Tháp Mười Tầng</t>
         </is>
       </c>
       <c r="N451" t="inlineStr">
@@ -32082,7 +32082,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Never-ending Night</t>
+          <t>Đêm Vĩnh Hằng</t>
         </is>
       </c>
       <c r="N452" t="inlineStr">
@@ -32152,7 +32152,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Beringal's Rage</t>
+          <t>Cơn Thịnh Nộ Beringal</t>
         </is>
       </c>
       <c r="N453" t="inlineStr">
@@ -32222,7 +32222,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Mourning Aix's Dance</t>
+          <t>Điệu Nhảy Của Mourning Aix</t>
         </is>
       </c>
       <c r="N454" t="inlineStr">
@@ -32292,7 +32292,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Mech Evolution</t>
+          <t>Tiến Hóa Cơ Khí</t>
         </is>
       </c>
       <c r="N455" t="inlineStr">
@@ -32362,7 +32362,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Inferno Valiance</t>
+          <t>Dũng Khí Hỏa Diêm</t>
         </is>
       </c>
       <c r="N456" t="inlineStr">
@@ -32432,7 +32432,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Bản Hợp Xướng Vạn Người</t>
+          <t>Đại Hợp Xướng Vô Tận</t>
         </is>
       </c>
       <c r="N457" t="inlineStr">
@@ -32502,7 +32502,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Scarred Sincerity</t>
+          <t>Chân Thành Đầy Vết Thương</t>
         </is>
       </c>
       <c r="N458" t="inlineStr">
@@ -32642,7 +32642,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Bell-Bearer's Duty</t>
+          <t>Nhiệm Vụ Người Mang Chuông</t>
         </is>
       </c>
       <c r="N460" t="inlineStr">
@@ -32712,7 +32712,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Daybreak Arises</t>
+          <t>Bình Minh Ló Dạng</t>
         </is>
       </c>
       <c r="N461" t="inlineStr">
@@ -32782,7 +32782,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>De Sophisticis Elenchis / Sophistical Refutations</t>
+          <t>Phản Bác Ngụy Biện</t>
         </is>
       </c>
       <c r="N462" t="inlineStr">
@@ -32852,7 +32852,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Khát Khao Nặng Trĩu</t>
+          <t>Khát Khao Nặng Lòng</t>
         </is>
       </c>
       <c r="N463" t="inlineStr">
@@ -32922,7 +32922,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Nhạc nền này có thể mở khóa từ Sự kiện Thường trực: Giấc Mộng Sâu</t>
+          <t>Nhạc nền này có thể mở khóa từ Sự kiện Thường trực: *Giấc Mơ Sâu Thẳm*.</t>
         </is>
       </c>
       <c r="N464" t="inlineStr">
@@ -32992,7 +32992,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Nhạc nền này có thể mở khóa từ Sự kiện Thường trực: Giấc Mộng Sâu</t>
+          <t>Nhạc nền này có thể mở khóa từ Sự kiện Thường trực: *Giấc Mơ Sâu Thẳm*.</t>
         </is>
       </c>
       <c r="N465" t="inlineStr">
@@ -33062,7 +33062,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Nhạc nền này có thể mở khóa từ Sự kiện Thường trực: Giấc Mộng Sâu</t>
+          <t>Nhạc nền này có thể mở khóa từ Sự kiện Thường trực: *Giấc Mơ Sâu Thẳm*.</t>
         </is>
       </c>
       <c r="N466" t="inlineStr">
@@ -33132,7 +33132,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Nhạc nền này có thể mở khóa từ Sự kiện Thường trực: Giấc Mộng Sâu</t>
+          <t>Nhạc nền này có thể mở khóa từ Sự kiện Thường trực: *Giấc Mơ Sâu Thẳm*.</t>
         </is>
       </c>
       <c r="N467" t="inlineStr">
@@ -33202,7 +33202,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Nhạc nền này có thể mở khóa từ Sự kiện Thường trực: Giấc Mộng Sâu</t>
+          <t>Nhạc nền này có thể mở khóa từ Sự kiện Thường trực: *Giấc Mơ Sâu Thẳm*.</t>
         </is>
       </c>
       <c r="N468" t="inlineStr">
@@ -33272,7 +33272,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Nhạc nền này có thể mở khóa từ Sự kiện Thường trực: Giấc Mộng Sâu</t>
+          <t>Nhạc nền này có thể mở khóa từ Sự kiện Thường trực: *Giấc Mơ Sâu Thẳm*.</t>
         </is>
       </c>
       <c r="N469" t="inlineStr">
@@ -33342,7 +33342,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Nhạc nền này có thể mở khóa từ Sự kiện Thường trực: Giấc Mộng Sâu</t>
+          <t>Nhạc nền này có thể mở khóa từ Sự kiện Thường trực: *Giấc Mơ Sâu Thẳm*.</t>
         </is>
       </c>
       <c r="N470" t="inlineStr">
@@ -33412,7 +33412,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Nhạc nền này có thể mở khóa từ Sự kiện Thường trực: Giấc Mộng Sâu</t>
+          <t>Nhạc nền này có thể mở khóa từ Sự kiện Thường trực: *Giấc Mơ Sâu Thẳm*.</t>
         </is>
       </c>
       <c r="N471" t="inlineStr">
@@ -33482,7 +33482,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Nhạc nền này có thể mở khóa từ Sự kiện Thường trực: Giấc Mộng Sâu</t>
+          <t>Nhạc nền này có thể mở khóa từ Sự kiện Thường trực: *Giấc Mơ Sâu Thẳm*.</t>
         </is>
       </c>
       <c r="N472" t="inlineStr">
@@ -33552,7 +33552,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Nhạc nền này có thể mở khóa từ Sự kiện Thường trực: Giấc Mộng Sâu</t>
+          <t>Nhạc nền này có thể mở khóa từ Sự kiện Thường trực: *Giấc Mơ Sâu Thẳm*.</t>
         </is>
       </c>
       <c r="N473" t="inlineStr">
@@ -33622,7 +33622,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Eversinging Song</t>
+          <t>Khúc Ca Trường Tồn</t>
         </is>
       </c>
       <c r="N474" t="inlineStr">
@@ -33692,7 +33692,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Khi Chim Lướt Trên Bầu Trời</t>
+          <t>Khi chim lướt qua bầu trời</t>
         </is>
       </c>
       <c r="N475" t="inlineStr">
@@ -33762,7 +33762,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Shallow</t>
+          <t>Nông cạn</t>
         </is>
       </c>
       <c r="N476" t="inlineStr">
@@ -33832,7 +33832,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Deep</t>
+          <t>Sâu Thẳm</t>
         </is>
       </c>
       <c r="N477" t="inlineStr">
@@ -33902,7 +33902,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Abyssal</t>
+          <t>Vực Sâu</t>
         </is>
       </c>
       <c r="N478" t="inlineStr">
@@ -33972,7 +33972,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Oceanic</t>
+          <t>Hải Dương</t>
         </is>
       </c>
       <c r="N479" t="inlineStr">
@@ -34042,7 +34042,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Wonder Bubble</t>
+          <t>Bong Bóng Kỳ Diệu</t>
         </is>
       </c>
       <c r="N480" t="inlineStr">
@@ -34112,7 +34112,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>When Spring Returns</t>
+          <t>Khi Xuân Trở Lại</t>
         </is>
       </c>
       <c r="N481" t="inlineStr">
@@ -34182,7 +34182,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>How Time Flies</t>
+          <t>Thời gian trôi qua nhanh thật đấy</t>
         </is>
       </c>
       <c r="N482" t="inlineStr">
@@ -34252,7 +34252,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Tuyết Cuối Mùa Đông</t>
+          <t>Những Bông Tuyết Cuối Mùa Đông</t>
         </is>
       </c>
       <c r="N483" t="inlineStr">
@@ -34322,7 +34322,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>To Cat's Eye</t>
+          <t>Đến Mắt Mèo</t>
         </is>
       </c>
       <c r="N484" t="inlineStr">
@@ -34392,7 +34392,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Vở Kịch Dành Cho Em</t>
+          <t>Một Vở Kịch Dành Cho Em</t>
         </is>
       </c>
       <c r="N485" t="inlineStr">
@@ -34462,7 +34462,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>When Spring Returns</t>
+          <t>Khi Xuân Trở Lại</t>
         </is>
       </c>
       <c r="N486" t="inlineStr">
@@ -34532,7 +34532,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>How Time Flies</t>
+          <t>Thời gian trôi qua nhanh thật đấy</t>
         </is>
       </c>
       <c r="N487" t="inlineStr">
@@ -34602,7 +34602,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Tuyết Cuối Mùa Đông</t>
+          <t>Những Bông Tuyết Cuối Mùa Đông</t>
         </is>
       </c>
       <c r="N488" t="inlineStr">
@@ -34672,7 +34672,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>To Cat's Eye</t>
+          <t>Đến Mắt Mèo</t>
         </is>
       </c>
       <c r="N489" t="inlineStr">
@@ -34742,7 +34742,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Vở Kịch Dành Cho Em</t>
+          <t>Một Vở Kịch Dành Cho Em</t>
         </is>
       </c>
       <c r="N490" t="inlineStr">
@@ -34812,7 +34812,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Hiện tại bạn không thể sử dụng chức năng này</t>
+          <t>Hiện tại bạn không thể sử dụng chức năng này.</t>
         </is>
       </c>
       <c r="N491" t="inlineStr">
@@ -34882,7 +34882,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Hiện tại bạn không thể sử dụng chức năng này</t>
+          <t>Hiện tại bạn không thể sử dụng chức năng này.</t>
         </is>
       </c>
       <c r="N492" t="inlineStr">
@@ -34952,7 +34952,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Invitation Progress:</t>
+          <t>Tiến trình mời:</t>
         </is>
       </c>
       <c r="N493" t="inlineStr">
@@ -35092,7 +35092,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>Đi thôi</t>
         </is>
       </c>
       <c r="N495" t="inlineStr">
@@ -35162,7 +35162,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Xác Nhận</t>
+          <t>Xác nhận</t>
         </is>
       </c>
       <c r="N496" t="inlineStr">
@@ -35232,7 +35232,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Show Custom Marker</t>
+          <t>Hiển thị Điểm đánh dấu Tùy chỉnh</t>
         </is>
       </c>
       <c r="N497" t="inlineStr">
@@ -35302,7 +35302,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Show Completed Challenges</t>
+          <t>Hiển thị Thử thách Đã hoàn thành</t>
         </is>
       </c>
       <c r="N498" t="inlineStr">
@@ -35442,7 +35442,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Có thể dùng làm Ảnh Đại Diện Hồ Sơ</t>
+          <t>Có thể dùng làm Ảnh Đại Diện Hồ Sơ của bạn</t>
         </is>
       </c>
       <c r="N500" t="inlineStr">
@@ -35512,7 +35512,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Avatar</t>
+          <t>Hóa Thân</t>
         </is>
       </c>
       <c r="N501" t="inlineStr">
